--- a/tests/fixtures/ml-real-publish-embedded.xlsx
+++ b/tests/fixtures/ml-real-publish-embedded.xlsx
@@ -4,8 +4,6 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
-    <sheet name="Imagenes" sheetId="2" r:id="rId2"/>
-    <sheet name="Instrucciones" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -75,6 +73,163 @@
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,36 +556,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:AD3"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="23.83203125" customWidth="1"/>
-    <col min="3" max="3" width="20.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" customWidth="1"/>
-    <col min="9" max="9" width="20.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
-    <col min="11" max="11" width="20.83203125" customWidth="1"/>
-    <col min="12" max="12" width="22.83203125" customWidth="1"/>
-    <col min="13" max="13" width="20.83203125" customWidth="1"/>
-    <col min="14" max="14" width="20.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="20.83203125" customWidth="1"/>
-    <col min="18" max="18" width="23.83203125" customWidth="1"/>
-    <col min="19" max="19" width="20.83203125" customWidth="1"/>
-    <col min="20" max="20" width="20.83203125" customWidth="1"/>
-    <col min="21" max="21" width="23.83203125" customWidth="1"/>
-    <col min="22" max="22" width="20.83203125" customWidth="1"/>
-    <col min="23" max="23" width="20.83203125" customWidth="1"/>
-    <col min="24" max="24" width="23.83203125" customWidth="1"/>
-    <col min="25" max="25" width="21.83203125" customWidth="1"/>
-    <col min="26" max="26" width="27.83203125" customWidth="1"/>
-    <col min="27" max="27" width="20.83203125" customWidth="1"/>
-    <col min="28" max="28" width="20.83203125" customWidth="1"/>
-    <col min="29" max="29" width="20.83203125" customWidth="1"/>
-    <col min="30" max="30" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="21.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="20.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="18" width="21.83203125" customWidth="1"/>
+    <col min="19" max="19" width="18.83203125" customWidth="1"/>
+    <col min="20" max="20" width="18.83203125" customWidth="1"/>
+    <col min="21" max="21" width="21.83203125" customWidth="1"/>
+    <col min="22" max="22" width="18.83203125" customWidth="1"/>
+    <col min="23" max="23" width="18.83203125" customWidth="1"/>
+    <col min="24" max="24" width="21.83203125" customWidth="1"/>
+    <col min="25" max="25" width="19.83203125" customWidth="1"/>
+    <col min="26" max="26" width="25.83203125" customWidth="1"/>
+    <col min="27" max="27" width="18.83203125" customWidth="1"/>
+    <col min="28" max="28" width="18.83203125" customWidth="1"/>
+    <col min="29" max="29" width="18.83203125" customWidth="1"/>
+    <col min="30" max="30" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,10 +739,10 @@
         <v>no</v>
       </c>
       <c r="T2" t="str">
-        <v>refrigerator-front-1200.png|refrigerator-open-1200.png</v>
+        <v/>
       </c>
       <c r="U2" t="str">
-        <v>Heladera Samsung No Frost RT29FARADWW de 290 litros. Tecnologia No Frost: elimina la escarcha automaticamente. Capacidad total: 290 litros. Incluye garantia oficial Samsung de 12 meses.</v>
+        <v>Heladera Samsung No Frost RT29FARADWW de 290 litros. Tecnologia No Frost. Incluye garantia oficial Samsung de 12 meses.</v>
       </c>
       <c r="V2" t="str">
         <v>7709545018831</v>
@@ -676,10 +831,10 @@
         <v>no</v>
       </c>
       <c r="T3" t="str">
-        <v>microwave-front-1200.png|microwave-side-1200.png</v>
+        <v/>
       </c>
       <c r="U3" t="str">
-        <v>Microondas Samsung MS23K3513AW de 23 litros y 1150 watts. 5 niveles de potencia ajustables. Incluye garantia oficial Samsung de 12 meses.</v>
+        <v>Microondas Samsung MS23K3513AW de 23 litros y 1150 watts. 5 niveles de potencia. Garantia oficial Samsung.</v>
       </c>
       <c r="V3" t="str">
         <v/>
@@ -713,162 +868,6 @@
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:AD3"/>
   </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <cols>
-    <col min="1" max="1" width="35.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>nombre_archivo</v>
-      </c>
-      <c r="B1" t="str">
-        <v>base64_data</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>refrigerator-front-1200.png</v>
-      </c>
-      <c r="B2" t="str">
-        <v>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABLAAAASwCAIAAABkQySYAABSeklEQVR4AezXQQEAAAgCMfuXxiA3GzD8cHMECBAgQIAAAQIECBAgkBS4ZGqhCRAgQIAAAQIECBAgQGAGoScgQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgACBb7+OCQAAABCE9W9NEBbB6SMBh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgACBACJE7hWLr0/XAAAAAElFTkSuQmCC</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>refrigerator-open-1200.png</v>
-      </c>
-      <c r="B3" t="str">
-        <v>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABLAAAASwCAIAAABkQySYAABSeklEQVR4AezXQQEAAAgCMfuXxiA3GzD8cHMECBAgQIAAAQIECBAgkBS4ZGqhCRAgQIAAAQIECBAgQGAGoScgQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgACBb7+OCQAAABCE9W9NEBbB6SMBh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgACBACJE7hWLr0/XAAAAAElFTkSuQmCC</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>microwave-front-1200.png</v>
-      </c>
-      <c r="B4" t="str">
-        <v>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABLAAAASwCAIAAABkQySYAABSeklEQVR4AezXQQEAAAgCMfuXxiA3GzD8cHMECBAgQIAAAQIECBAgkBS4ZGqhCRAgQIAAAQIECBAgQGAGoScgQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgACBb7+OCQAAABCE9W9NEBbB6SMBh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgACBACJE7hWLr0/XAAAAAElFTkSuQmCC</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>microwave-side-1200.png</v>
-      </c>
-      <c r="B5" t="str">
-        <v>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAABLAAAASwCAIAAABkQySYAABSeklEQVR4AezXQQEAAAgCMfuXxiA3GzD8cHMECBAgQIAAAQIECBAgkBS4ZGqhCRAgQIAAAQIECBAgQGAGoScgQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgAABAgahHyBAgAABAgQIECBAgEBUwCCMFi82AQIECBAgQIAAAQIEDEI/QIAAAQIECBAgQIAAgaiAQRgtXmwCBAgQIECAAAECBAgYhH6AAAECBAgQIECAAAECUQGDMFq82AQIECBAgAABAgQIEDAI/QABAgQIECBAgAABAgSiAgZhtHixCRAgQIAAAQIECBAgYBD6AQIECBAgQIAAAQIECEQFDMJo8WITIECAAAECBAgQIEDAIPQDBAgQIECAAAECBAgQiAoYhNHixSZAgAABAgQIECBAgIBB6AcIECBAgAABAgQIECAQFTAIo8WLTYAAAQIECBAgQIAAAYPQDxAgQIAAAQIECBAgQCAqYBBGixebAAECBAgQIECAAAECBqEfIECAAAECBAgQIECAQFTAIIwWLzYBAgQIECBAgAABAgQMQj9AgAABAgQIECBAgACBqIBBGC1ebAIECBAgQIAAAQIECBiEfoAAAQIECBAgQIAAAQJRAYMwWrzYBAgQIECAAAECBAgQMAj9AAECBAgQIECAAAECBKICBmG0eLEJECBAgAABAgQIECBgEPoBAgQIECBAgAABAgQIRAUMwmjxYhMgQIAAAQIECBAgQMAg9AMECBAgQIAAAQIECBCIChiE0eLFJkCAAAECBAgQIECAgEHoBwgQIECAAAECBAgQIBAVMAijxYtNgAABAgQIECBAgAABg9APECBAgAABAgQIECBAICpgEEaLF5sAAQIECBAgQIAAAQIGoR8gQIAAAQIECBAgQIBAVMAgjBYvNgECBAgQIECAAAECBAxCP0CAAAECBAgQIECAAIGogEEYLV5sAgQIECBAgAABAgQIGIR+gAABAgQIECBAgAABAlEBgzBavNgECBAgQIAAAQIECBAwCP0AAQIECBAgQIAAAQIEogIGYbR4sQkQIECAAAECBAgQIGAQ+gECBAgQIECAAAECBAhEBQzCaPFiEyBAgAABAgQIECBAwCD0AwQIECBAgAABAgQIEIgKGITR4sUmQIAAAQIECBAgQICAQegHCBAgQIAAAQIECBAgEBUwCKPFi02AAAECBAgQIECAAAGD0A8QIECAAAECBAgQIEAgKmAQRosXmwABAgQIECBAgACBb7+OCQAAABCE9W9NEBbB6SMBh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgAABh9AGCBAgQIAAAQIECBAgMBVwCKfFi02AAAECBAgQIECAAAGH0AYIECBAgAABAgQIECAwFXAIp8WLTYAAAQIECBAgQIAAAYfQBggQIECAAAECBAgQIDAVcAinxYtNgAABAgQIECBAgACBACJE7hWLr0/XAAAAAElFTkSuQmCC</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
-  <cols>
-    <col min="1" max="1" width="55.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ARCHIVO DE TEST — UN SOLO ARCHIVO, IMÁGENES INCLUIDAS</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Las 4 imágenes PNG están embebidas en la hoja "Imagenes" de este archivo.</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Subí SOLO ESTE archivo en FastPublisher → modo bulk → "Subir archivo".</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Las imágenes se detectan automáticamente. No necesitás subir PNGs por separado.</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>PRODUCTOS</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Heladera Samsung No Frost 290L Blanca — $450.000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Microondas Samsung 23L 1150W Blanco  — $115.000</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>IMÁGENES EMBEBIDAS (hoja "Imagenes")</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>refrigerator-front-1200.png</v>
-      </c>
-      <c r="B12" t="str">
-        <v>✓ incluida</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>refrigerator-open-1200.png</v>
-      </c>
-      <c r="B13" t="str">
-        <v>✓ incluida</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>microwave-front-1200.png</v>
-      </c>
-      <c r="B14" t="str">
-        <v>✓ incluida</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>microwave-side-1200.png</v>
-      </c>
-      <c r="B15" t="str">
-        <v>✓ incluida</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B15"/>
-  </ignoredErrors>
+  <drawing r:id="rId100"/>
 </worksheet>
 </file>